--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-specimen-common.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-specimen-common.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Specimen</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Specimen|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -434,7 +434,7 @@
     <t>Specimen.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -472,7 +472,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -530,7 +530,7 @@
     <t>人間の言語</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -702,7 +702,7 @@
     <t>標本のタイプ</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0487</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0487|2.0.0</t>
   </si>
   <si>
     <t>.code</t>
@@ -717,7 +717,7 @@
     <t>Specimen.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Substance|Location)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Substance|4.0.1|Location|4.0.1)
 </t>
   </si>
   <si>
@@ -761,7 +761,7 @@
     <t>Specimen.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -780,7 +780,7 @@
     <t>Specimen.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -842,7 +842,7 @@
     <t>Specimen.collection.collector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -899,7 +899,7 @@
     <t>Specimen.collection.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -927,7 +927,7 @@
     <t>採取方法</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -948,7 +948,7 @@
     <t>ユースケースでは、ボディサイトをインラインコード化された要素の代わりに個別のリソースとして処理する必要がある場合（たとえば、個別に識別および追跡するため）、標準の拡張[BodySite]（Extension-BodySite.html）を使用します。 / If the use case requires  BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -979,7 +979,7 @@
     <t>患者の絶食状況</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0916</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0916|2.0.0</t>
   </si>
   <si>
     <t>OBR-</t>
@@ -1030,13 +1030,13 @@
     <t>材料に対する処理</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure|4.0.1</t>
   </si>
   <si>
     <t>Specimen.processing.additive</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Substance)
+    <t xml:space="preserve">Reference(Substance|4.0.1)
 </t>
   </si>
   <si>
@@ -1118,7 +1118,7 @@
     <t>容器種別</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-container-type</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-container-type|4.0.1</t>
   </si>
   <si>
     <t>SPM-27</t>
@@ -1155,7 +1155,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance)</t>
+Reference(Substance|4.0.1)</t>
   </si>
   <si>
     <t>採取容器の添加物（ CodeableConcept または Reference(Substance) のどちらか）</t>
@@ -1167,7 +1167,7 @@
     <t>採取容器の添加物</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0371</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0371|2.0.0</t>
   </si>
   <si>
     <t>.scopesRole[classCode=ADTV].player</t>
@@ -1194,7 +1194,7 @@
     <t>材料の状態を説明するコード</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0493</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0493|2.0.0</t>
   </si>
   <si>
     <t>SPM-24</t>
@@ -1546,7 +1546,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="42.890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="65.53515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1561,7 +1561,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="34.8515625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.75" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.27734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-specimen-common.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-specimen-common.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Specimen|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Specimen</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -434,7 +434,7 @@
     <t>Specimen.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -472,7 +472,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -530,7 +530,7 @@
     <t>人間の言語</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -702,7 +702,7 @@
     <t>標本のタイプ</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0487|2.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0487</t>
   </si>
   <si>
     <t>.code</t>
@@ -717,7 +717,7 @@
     <t>Specimen.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Substance|4.0.1|Location|4.0.1)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Substance|Location)
 </t>
   </si>
   <si>
@@ -761,7 +761,7 @@
     <t>Specimen.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
@@ -780,7 +780,7 @@
     <t>Specimen.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(ServiceRequest)
 </t>
   </si>
   <si>
@@ -842,7 +842,7 @@
     <t>Specimen.collection.collector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
 </t>
   </si>
   <si>
@@ -899,7 +899,7 @@
     <t>Specimen.collection.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -927,7 +927,7 @@
     <t>採取方法</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -948,7 +948,7 @@
     <t>ユースケースでは、ボディサイトをインラインコード化された要素の代わりに個別のリソースとして処理する必要がある場合（たとえば、個別に識別および追跡するため）、標準の拡張[BodySite]（Extension-BodySite.html）を使用します。 / If the use case requires  BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -979,7 +979,7 @@
     <t>患者の絶食状況</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0916|2.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0916</t>
   </si>
   <si>
     <t>OBR-</t>
@@ -1030,13 +1030,13 @@
     <t>材料に対する処理</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure</t>
   </si>
   <si>
     <t>Specimen.processing.additive</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Substance|4.0.1)
+    <t xml:space="preserve">Reference(Substance)
 </t>
   </si>
   <si>
@@ -1118,7 +1118,7 @@
     <t>容器種別</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-container-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-container-type</t>
   </si>
   <si>
     <t>SPM-27</t>
@@ -1155,7 +1155,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance|4.0.1)</t>
+Reference(Substance)</t>
   </si>
   <si>
     <t>採取容器の添加物（ CodeableConcept または Reference(Substance) のどちらか）</t>
@@ -1167,7 +1167,7 @@
     <t>採取容器の添加物</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0371|2.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0371</t>
   </si>
   <si>
     <t>.scopesRole[classCode=ADTV].player</t>
@@ -1194,7 +1194,7 @@
     <t>材料の状態を説明するコード</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0493|2.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0493</t>
   </si>
   <si>
     <t>SPM-24</t>
@@ -1546,7 +1546,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="65.53515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="42.890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1561,7 +1561,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="34.8515625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.27734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.75" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
